--- a/runs/RELX/2026-10-14/bear/scratch/s_stack_331/out/dcf.xlsx
+++ b/runs/RELX/2026-10-14/bear/scratch/s_stack_331/out/dcf.xlsx
@@ -539,11 +539,11 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>0.08807371450558467</v>
+        <v>0.09046896835686265</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>PM rule: return on new investment 10.6% (value driver formula, briefs/RELX.yaml)</t>
+          <t>PM rule: return on new investment 9.9% (value driver formula, briefs/RELX.yaml)</t>
         </is>
       </c>
     </row>
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.05</v>
+        <v>0.042</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="I15" s="4" t="n">
-        <v>1654.903144880593</v>
+        <v>1701.798340131523</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v/>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.103145</v>
+        <v>0.0953618</v>
       </c>
     </row>
     <row r="18">
@@ -1420,7 +1420,7 @@
         <v/>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.09615342190000001</v>
+        <v>0.089367872476</v>
       </c>
     </row>
     <row r="20">
@@ -1434,7 +1434,7 @@
         <v/>
       </c>
       <c r="C20" s="4" t="n">
-        <v>9007.532115141539</v>
+        <v>9144.250894037257</v>
       </c>
     </row>
     <row r="21">
@@ -1448,7 +1448,7 @@
         <v/>
       </c>
       <c r="C21" s="4" t="n">
-        <v>2597.807832329981</v>
+        <v>2568.618066057131</v>
       </c>
     </row>
     <row r="22">
@@ -1462,7 +1462,7 @@
         <v/>
       </c>
       <c r="C22" s="4" t="n">
-        <v>32011.06954591622</v>
+        <v>34539.35120822605</v>
       </c>
     </row>
     <row r="23">
@@ -1476,7 +1476,7 @@
         <v/>
       </c>
       <c r="C23" s="4" t="n">
-        <v>21177.71683760322</v>
+        <v>23497.87786565447</v>
       </c>
     </row>
     <row r="24">
@@ -1490,7 +1490,7 @@
         <v/>
       </c>
       <c r="C24" s="4" t="n">
-        <v>30185.24895274476</v>
+        <v>32642.12875969173</v>
       </c>
     </row>
     <row r="25">
@@ -1518,7 +1518,7 @@
         <v/>
       </c>
       <c r="C26" s="4" t="n">
-        <v>23188.24895274476</v>
+        <v>25645.12875969173</v>
       </c>
     </row>
     <row r="27">
@@ -1532,7 +1532,7 @@
         <v/>
       </c>
       <c r="C27" s="4" t="n">
-        <v>21769.03894521212</v>
+        <v>24269.12698897315</v>
       </c>
     </row>
     <row r="28">
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="C28" s="4" t="n">
-        <v>12.48400282915025</v>
+        <v>13.91774118985551</v>
       </c>
     </row>
     <row r="29">
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="C29" s="4" t="n">
-        <v>1248.400282915025</v>
+        <v>1391.774118985551</v>
       </c>
     </row>
     <row r="30">
@@ -1574,7 +1574,7 @@
         <v/>
       </c>
       <c r="C30" s="6" t="n">
-        <v>-0.5494766211</v>
+        <v>-0.4977357925</v>
       </c>
     </row>
   </sheetData>
